--- a/artfynd/A 37971-2025 artfynd.xlsx
+++ b/artfynd/A 37971-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>128466941</v>
       </c>
       <c r="B3" t="n">
-        <v>92676</v>
+        <v>92678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>128466503</v>
       </c>
       <c r="B4" t="n">
-        <v>91990</v>
+        <v>91992</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37971-2025 artfynd.xlsx
+++ b/artfynd/A 37971-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128467429</v>
       </c>
       <c r="B2" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128466941</v>
       </c>
       <c r="B3" t="n">
-        <v>92678</v>
+        <v>92770</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>128466503</v>
       </c>
       <c r="B4" t="n">
-        <v>91992</v>
+        <v>92084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37971-2025 artfynd.xlsx
+++ b/artfynd/A 37971-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128467429</v>
       </c>
       <c r="B2" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128466941</v>
       </c>
       <c r="B3" t="n">
-        <v>92770</v>
+        <v>92782</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>128466503</v>
       </c>
       <c r="B4" t="n">
-        <v>92084</v>
+        <v>92096</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37971-2025 artfynd.xlsx
+++ b/artfynd/A 37971-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>128466941</v>
       </c>
       <c r="B3" t="n">
-        <v>92782</v>
+        <v>92784</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>128466503</v>
       </c>
       <c r="B4" t="n">
-        <v>92096</v>
+        <v>92098</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37971-2025 artfynd.xlsx
+++ b/artfynd/A 37971-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>128466941</v>
       </c>
       <c r="B3" t="n">
-        <v>92784</v>
+        <v>92785</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>128466503</v>
       </c>
       <c r="B4" t="n">
-        <v>92098</v>
+        <v>92099</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37971-2025 artfynd.xlsx
+++ b/artfynd/A 37971-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128467429</v>
       </c>
       <c r="B2" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128466941</v>
       </c>
       <c r="B3" t="n">
-        <v>92785</v>
+        <v>92812</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>128466503</v>
       </c>
       <c r="B4" t="n">
-        <v>92099</v>
+        <v>92126</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37971-2025 artfynd.xlsx
+++ b/artfynd/A 37971-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>128466941</v>
       </c>
       <c r="B3" t="n">
-        <v>92812</v>
+        <v>92823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +807,12 @@
       <c r="E3" t="n">
         <v>5449</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>9</t>
@@ -915,7 +906,7 @@
         <v>128466503</v>
       </c>
       <c r="B4" t="n">
-        <v>92126</v>
+        <v>92136</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37971-2025 artfynd.xlsx
+++ b/artfynd/A 37971-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128467429</v>
       </c>
       <c r="B2" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128466941</v>
       </c>
       <c r="B3" t="n">
-        <v>92823</v>
+        <v>92827</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>128466503</v>
       </c>
       <c r="B4" t="n">
-        <v>92136</v>
+        <v>92140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37971-2025 artfynd.xlsx
+++ b/artfynd/A 37971-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128467429</v>
       </c>
       <c r="B2" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128466941</v>
       </c>
       <c r="B3" t="n">
-        <v>92827</v>
+        <v>92832</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>128466503</v>
       </c>
       <c r="B4" t="n">
-        <v>92140</v>
+        <v>92145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
